--- a/raw_benchmarking_data.xlsx
+++ b/raw_benchmarking_data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://imperiallondon-my.sharepoint.com/personal/whl22_ic_ac_uk/Documents/Year 4/CIVE70009 FYP/Github push/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{08C9384B-328C-394D-B8AE-69874EC1DD6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="8_{08C9384B-328C-394D-B8AE-69874EC1DD6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{180E7A1E-D552-6E43-89ED-778AEE742FD1}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="19620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -95,15 +95,9 @@
     <t>Index (1-5)</t>
   </si>
   <si>
-    <t>Median temperature</t>
-  </si>
-  <si>
     <t>∘C</t>
   </si>
   <si>
-    <t>Median Humidity</t>
-  </si>
-  <si>
     <t>Economic</t>
   </si>
   <si>
@@ -272,9 +266,6 @@
     <t>Number of rainy days per year</t>
   </si>
   <si>
-    <t>Median rainfall per year</t>
-  </si>
-  <si>
     <t>days</t>
   </si>
   <si>
@@ -291,6 +282,15 @@
   </si>
   <si>
     <t>Network Centrality</t>
+  </si>
+  <si>
+    <t>Mean Humidity</t>
+  </si>
+  <si>
+    <t>Mean rainfall per year</t>
+  </si>
+  <si>
+    <t>Mean temperature</t>
   </si>
 </sst>
 </file>
@@ -348,7 +348,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -394,18 +394,6 @@
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -765,73 +753,71 @@
         <v>2</v>
       </c>
       <c r="D1" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="F1" s="13" t="s">
         <v>36</v>
-      </c>
-      <c r="E1" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="F1" s="13" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="17"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="E2" s="11"/>
     </row>
     <row r="3" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B3" s="19" t="s">
-        <v>67</v>
-      </c>
-      <c r="C3" s="19" t="s">
+      <c r="B3" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="18">
+      <c r="D3" s="16">
         <v>10</v>
       </c>
-      <c r="E3" s="18">
+      <c r="E3" s="16">
         <v>44.2</v>
       </c>
-      <c r="F3" s="18">
+      <c r="F3" s="16">
         <v>42.2</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B4" s="19" t="s">
-        <v>39</v>
-      </c>
-      <c r="C4" s="19" t="s">
+      <c r="B4" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="17">
+      <c r="D4" s="10">
         <v>1.5</v>
       </c>
-      <c r="E4" s="17">
+      <c r="E4" s="10">
         <v>3.59</v>
       </c>
-      <c r="F4" s="17">
+      <c r="F4" s="10">
         <v>2.2999999999999998</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B5" s="19" t="s">
-        <v>40</v>
-      </c>
-      <c r="C5" s="19" t="s">
+      <c r="B5" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="17">
+      <c r="D5" s="10">
         <v>7</v>
       </c>
-      <c r="E5" s="17">
+      <c r="E5" s="10">
         <v>5</v>
       </c>
-      <c r="F5" s="17">
+      <c r="F5" s="10">
         <v>6</v>
       </c>
     </row>
@@ -854,7 +840,7 @@
     </row>
     <row r="7" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B7" s="3" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C7" s="3"/>
       <c r="D7" s="10">
@@ -869,18 +855,18 @@
     </row>
     <row r="8" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B8" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D8" s="17">
+      <c r="D8" s="10">
         <v>91.7</v>
       </c>
-      <c r="E8" s="17">
+      <c r="E8" s="10">
         <v>99.9</v>
       </c>
-      <c r="F8" s="17">
+      <c r="F8" s="10">
         <v>99.9</v>
       </c>
     </row>
@@ -891,13 +877,13 @@
       <c r="C9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="17">
+      <c r="D9" s="10">
         <v>1572</v>
       </c>
-      <c r="E9" s="17">
+      <c r="E9" s="10">
         <v>1115</v>
       </c>
-      <c r="F9" s="17">
+      <c r="F9" s="10">
         <v>744.3</v>
       </c>
     </row>
@@ -908,13 +894,13 @@
       <c r="C10" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="17">
+      <c r="D10" s="10">
         <v>272</v>
       </c>
-      <c r="E10" s="17">
+      <c r="E10" s="10">
         <v>98</v>
       </c>
-      <c r="F10" s="17">
+      <c r="F10" s="10">
         <v>143</v>
       </c>
     </row>
@@ -925,129 +911,120 @@
       <c r="C11" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D11" s="17">
+      <c r="D11" s="10">
         <v>63</v>
       </c>
-      <c r="E11" s="17">
+      <c r="E11" s="10">
         <v>18</v>
       </c>
-      <c r="F11" s="17">
+      <c r="F11" s="10">
         <v>28</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B12" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D12" s="18" t="s">
+      <c r="D12" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="E12" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="F12" s="16" t="s">
         <v>51</v>
-      </c>
-      <c r="E12" s="18" t="s">
-        <v>52</v>
-      </c>
-      <c r="F12" s="18" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B13" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D13" s="18" t="s">
+      <c r="D13" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="E13" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="F13" s="16" t="s">
         <v>48</v>
-      </c>
-      <c r="E13" s="18" t="s">
-        <v>49</v>
-      </c>
-      <c r="F13" s="18" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B14" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D14" s="18">
+      <c r="D14" s="16">
         <v>2.8</v>
       </c>
-      <c r="E14" s="18">
+      <c r="E14" s="16">
         <v>23.6</v>
       </c>
-      <c r="F14" s="18">
+      <c r="F14" s="16">
         <v>1.58</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B15" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D15" s="18">
+      <c r="D15" s="16">
         <v>0.2</v>
       </c>
-      <c r="E15" s="18">
+      <c r="E15" s="16">
         <v>10.130000000000001</v>
       </c>
-      <c r="F15" s="18">
+      <c r="F15" s="16">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="3"/>
-      <c r="D16" s="17"/>
-      <c r="E16" s="17"/>
-      <c r="F16" s="17"/>
     </row>
     <row r="17" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D17" s="17"/>
-      <c r="E17" s="17"/>
-      <c r="F17" s="17"/>
     </row>
     <row r="18" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D18" s="17">
+      <c r="D18" s="10">
         <v>2.5</v>
       </c>
-      <c r="E18" s="17">
+      <c r="E18" s="10">
         <v>5</v>
       </c>
-      <c r="F18" s="17">
+      <c r="F18" s="10">
         <v>4.7</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B19" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D19" s="17"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="17"/>
     </row>
     <row r="20" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B20" s="15" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C20" s="3"/>
       <c r="D20" s="10">
@@ -1062,7 +1039,7 @@
     </row>
     <row r="21" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B21" s="15" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C21" s="3"/>
       <c r="D21" s="10">
@@ -1077,7 +1054,7 @@
     </row>
     <row r="22" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B22" s="15" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C22" s="3"/>
       <c r="D22" s="10">
@@ -1092,7 +1069,7 @@
     </row>
     <row r="23" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B23" s="15" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C23" s="3"/>
       <c r="D23" s="10">
@@ -1107,7 +1084,7 @@
     </row>
     <row r="24" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B24" s="15" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C24" s="3"/>
       <c r="D24" s="10">
@@ -1122,7 +1099,7 @@
     </row>
     <row r="25" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B25" s="15" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C25" s="3"/>
       <c r="D25" s="10">
@@ -1159,10 +1136,10 @@
     </row>
     <row r="28" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B28" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C28" s="3" t="s">
         <v>20</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>21</v>
       </c>
       <c r="D28" s="10">
         <v>11.1</v>
@@ -1176,10 +1153,10 @@
     </row>
     <row r="29" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B29" s="3" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D29" s="10">
         <v>789</v>
@@ -1193,10 +1170,10 @@
     </row>
     <row r="30" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B30" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D30" s="10">
         <v>112</v>
@@ -1210,7 +1187,7 @@
     </row>
     <row r="31" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B31" s="3" t="s">
-        <v>22</v>
+        <v>83</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>12</v>
@@ -1227,7 +1204,7 @@
     </row>
     <row r="32" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B32" s="3" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>12</v>
@@ -1267,14 +1244,14 @@
     </row>
     <row r="35" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
     </row>
     <row r="36" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B36" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>10</v>
@@ -1291,7 +1268,7 @@
     </row>
     <row r="37" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B37" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>10</v>
@@ -1308,7 +1285,7 @@
     </row>
     <row r="38" spans="1:6" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B38" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>12</v>
@@ -1316,7 +1293,7 @@
     </row>
     <row r="39" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B39" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>12</v>
@@ -1333,7 +1310,7 @@
     </row>
     <row r="40" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B40" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C40" s="3"/>
       <c r="D40" s="10">
@@ -1348,7 +1325,7 @@
     </row>
     <row r="41" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B41" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C41" s="3" t="s">
         <v>12</v>
@@ -1365,7 +1342,7 @@
     </row>
     <row r="42" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B42" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C42" s="3" t="s">
         <v>12</v>
@@ -1382,7 +1359,7 @@
     </row>
     <row r="43" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B43" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>12</v>
@@ -1399,7 +1376,7 @@
     </row>
     <row r="44" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B44" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C44" s="3" t="s">
         <v>12</v>
@@ -1416,7 +1393,7 @@
     </row>
     <row r="45" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B45" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C45" s="3" t="s">
         <v>10</v>
@@ -1433,27 +1410,27 @@
     </row>
     <row r="46" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B46" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D46" s="10" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E46" s="10" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F46" s="10" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B47" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D47" s="10">
         <v>5</v>
@@ -1467,10 +1444,10 @@
     </row>
     <row r="48" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B48" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D48" s="10">
         <v>94.9</v>
@@ -1489,14 +1466,14 @@
     </row>
     <row r="50" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B50" s="3"/>
       <c r="C50" s="3"/>
     </row>
     <row r="51" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B51" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C51" s="3" t="s">
         <v>13</v>
@@ -1505,15 +1482,15 @@
         <v>3650</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F51" s="10" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B52" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C52" s="3" t="s">
         <v>13</v>
@@ -1522,15 +1499,15 @@
         <v>1900</v>
       </c>
       <c r="E52" s="10" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F52" s="10" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B53" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C53" s="3" t="s">
         <v>13</v>
@@ -1539,18 +1516,18 @@
         <v>201.6</v>
       </c>
       <c r="E53" s="11" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F53" s="11" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B54" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D54" s="10">
         <v>30</v>
@@ -1564,7 +1541,7 @@
     </row>
     <row r="55" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B55" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C55" s="3" t="s">
         <v>10</v>
@@ -1582,10 +1559,10 @@
     <row r="56" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A56" s="3"/>
       <c r="B56" s="3" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D56" s="16">
         <v>40.5</v>
@@ -1599,10 +1576,10 @@
     </row>
     <row r="57" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B57" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D57" s="10">
         <v>21</v>

--- a/raw_benchmarking_data.xlsx
+++ b/raw_benchmarking_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://imperiallondon-my.sharepoint.com/personal/whl22_ic_ac_uk/Documents/Year 4/CIVE70009 FYP/Github push/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="8_{08C9384B-328C-394D-B8AE-69874EC1DD6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{180E7A1E-D552-6E43-89ED-778AEE742FD1}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="8_{08C9384B-328C-394D-B8AE-69874EC1DD6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2E449CD5-AC01-5884-96E5-5C75DC4693DC}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="19620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -95,9 +95,15 @@
     <t>Index (1-5)</t>
   </si>
   <si>
+    <t>Median temperature</t>
+  </si>
+  <si>
     <t>∘C</t>
   </si>
   <si>
+    <t>Median Humidity</t>
+  </si>
+  <si>
     <t>Economic</t>
   </si>
   <si>
@@ -266,6 +272,9 @@
     <t>Number of rainy days per year</t>
   </si>
   <si>
+    <t>Median rainfall per year</t>
+  </si>
+  <si>
     <t>days</t>
   </si>
   <si>
@@ -282,15 +291,6 @@
   </si>
   <si>
     <t>Network Centrality</t>
-  </si>
-  <si>
-    <t>Mean Humidity</t>
-  </si>
-  <si>
-    <t>Mean rainfall per year</t>
-  </si>
-  <si>
-    <t>Mean temperature</t>
   </si>
 </sst>
 </file>
@@ -753,13 +753,13 @@
         <v>2</v>
       </c>
       <c r="D1" s="12" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F1" s="13" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -772,7 +772,7 @@
     </row>
     <row r="3" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B3" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>12</v>
@@ -789,7 +789,7 @@
     </row>
     <row r="4" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B4" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>4</v>
@@ -806,7 +806,7 @@
     </row>
     <row r="5" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B5" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>4</v>
@@ -840,7 +840,7 @@
     </row>
     <row r="7" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B7" s="3" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C7" s="3"/>
       <c r="D7" s="10">
@@ -855,7 +855,7 @@
     </row>
     <row r="8" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B8" s="3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>12</v>
@@ -923,41 +923,41 @@
     </row>
     <row r="12" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B12" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E12" s="16" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F12" s="16" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B13" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D13" s="16" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E13" s="16" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F13" s="16" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B14" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>13</v>
@@ -974,7 +974,7 @@
     </row>
     <row r="15" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B15" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>13</v>
@@ -999,7 +999,7 @@
     </row>
     <row r="18" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>10</v>
@@ -1016,7 +1016,7 @@
     </row>
     <row r="19" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B19" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>15</v>
@@ -1024,7 +1024,7 @@
     </row>
     <row r="20" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B20" s="15" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C20" s="3"/>
       <c r="D20" s="10">
@@ -1039,7 +1039,7 @@
     </row>
     <row r="21" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B21" s="15" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C21" s="3"/>
       <c r="D21" s="10">
@@ -1054,7 +1054,7 @@
     </row>
     <row r="22" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B22" s="15" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C22" s="3"/>
       <c r="D22" s="10">
@@ -1069,7 +1069,7 @@
     </row>
     <row r="23" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B23" s="15" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C23" s="3"/>
       <c r="D23" s="10">
@@ -1084,7 +1084,7 @@
     </row>
     <row r="24" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B24" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C24" s="3"/>
       <c r="D24" s="10">
@@ -1099,7 +1099,7 @@
     </row>
     <row r="25" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B25" s="15" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C25" s="3"/>
       <c r="D25" s="10">
@@ -1136,10 +1136,10 @@
     </row>
     <row r="28" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B28" s="3" t="s">
-        <v>85</v>
+        <v>20</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D28" s="10">
         <v>11.1</v>
@@ -1153,10 +1153,10 @@
     </row>
     <row r="29" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B29" s="3" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D29" s="10">
         <v>789</v>
@@ -1170,10 +1170,10 @@
     </row>
     <row r="30" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B30" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D30" s="10">
         <v>112</v>
@@ -1187,7 +1187,7 @@
     </row>
     <row r="31" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B31" s="3" t="s">
-        <v>83</v>
+        <v>22</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>12</v>
@@ -1204,7 +1204,7 @@
     </row>
     <row r="32" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B32" s="3" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>12</v>
@@ -1244,14 +1244,14 @@
     </row>
     <row r="35" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
     </row>
     <row r="36" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B36" s="3" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>10</v>
@@ -1268,7 +1268,7 @@
     </row>
     <row r="37" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B37" s="3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>10</v>
@@ -1285,7 +1285,7 @@
     </row>
     <row r="38" spans="1:6" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B38" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>12</v>
@@ -1293,7 +1293,7 @@
     </row>
     <row r="39" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B39" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>12</v>
@@ -1310,7 +1310,7 @@
     </row>
     <row r="40" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B40" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C40" s="3"/>
       <c r="D40" s="10">
@@ -1325,7 +1325,7 @@
     </row>
     <row r="41" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B41" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C41" s="3" t="s">
         <v>12</v>
@@ -1342,7 +1342,7 @@
     </row>
     <row r="42" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B42" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C42" s="3" t="s">
         <v>12</v>
@@ -1359,7 +1359,7 @@
     </row>
     <row r="43" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B43" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>12</v>
@@ -1376,7 +1376,7 @@
     </row>
     <row r="44" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B44" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C44" s="3" t="s">
         <v>12</v>
@@ -1393,7 +1393,7 @@
     </row>
     <row r="45" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B45" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C45" s="3" t="s">
         <v>10</v>
@@ -1410,27 +1410,27 @@
     </row>
     <row r="46" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B46" s="3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D46" s="10" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E46" s="10" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F46" s="10" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B47" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D47" s="10">
         <v>5</v>
@@ -1444,10 +1444,10 @@
     </row>
     <row r="48" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B48" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C48" s="3" t="s">
         <v>27</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>25</v>
       </c>
       <c r="D48" s="10">
         <v>94.9</v>
@@ -1466,14 +1466,14 @@
     </row>
     <row r="50" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B50" s="3"/>
       <c r="C50" s="3"/>
     </row>
     <row r="51" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B51" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C51" s="3" t="s">
         <v>13</v>
@@ -1482,15 +1482,15 @@
         <v>3650</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F51" s="10" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B52" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C52" s="3" t="s">
         <v>13</v>
@@ -1499,15 +1499,15 @@
         <v>1900</v>
       </c>
       <c r="E52" s="10" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F52" s="10" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B53" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C53" s="3" t="s">
         <v>13</v>
@@ -1516,18 +1516,18 @@
         <v>201.6</v>
       </c>
       <c r="E53" s="11" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F53" s="11" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B54" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D54" s="10">
         <v>30</v>
@@ -1541,7 +1541,7 @@
     </row>
     <row r="55" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B55" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C55" s="3" t="s">
         <v>10</v>
@@ -1559,10 +1559,10 @@
     <row r="56" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A56" s="3"/>
       <c r="B56" s="3" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D56" s="16">
         <v>40.5</v>
@@ -1576,10 +1576,10 @@
     </row>
     <row r="57" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B57" s="3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D57" s="10">
         <v>21</v>
